--- a/outputs/55060.xlsx
+++ b/outputs/55060.xlsx
@@ -350,47 +350,47 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -398,7 +398,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -406,15 +406,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -426,19 +426,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -450,7 +450,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -458,11 +458,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -470,59 +470,59 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -530,39 +530,39 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>

--- a/outputs/55060.xlsx
+++ b/outputs/55060.xlsx
@@ -1055,7 +1055,7 @@
       <c r="F23" s="50"/>
       <c r="G23" s="50"/>
       <c r="J23" s="51" t="str">
-        <f aca="false">IF(I12="","",I12)</f>
+        <f aca="false">I12</f>
         <v>January</v>
       </c>
       <c r="K23" s="51"/>
